--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128471245</v>
+        <v>128471246</v>
       </c>
       <c r="B6" t="n">
         <v>79111</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747607</v>
+        <v>747594</v>
       </c>
       <c r="R6" t="n">
-        <v>7457693</v>
+        <v>7457689</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128471246</v>
+        <v>128471245</v>
       </c>
       <c r="B7" t="n">
         <v>79111</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747594</v>
+        <v>747607</v>
       </c>
       <c r="R7" t="n">
-        <v>7457689</v>
+        <v>7457693</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128471249</v>
       </c>
       <c r="B2" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128471247</v>
       </c>
       <c r="B3" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128471232</v>
       </c>
       <c r="B4" t="n">
-        <v>95334</v>
+        <v>95427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128471248</v>
       </c>
       <c r="B5" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128471246</v>
       </c>
       <c r="B6" t="n">
-        <v>79111</v>
+        <v>79162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128471245</v>
       </c>
       <c r="B7" t="n">
-        <v>79111</v>
+        <v>79162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128471231</v>
       </c>
       <c r="B8" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128471250</v>
       </c>
       <c r="B9" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128471240</v>
       </c>
       <c r="B10" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128471228</v>
       </c>
       <c r="B11" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128471249</v>
       </c>
       <c r="B2" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128471247</v>
       </c>
       <c r="B3" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128471232</v>
       </c>
       <c r="B4" t="n">
-        <v>95427</v>
+        <v>95433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128471248</v>
       </c>
       <c r="B5" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128471246</v>
       </c>
       <c r="B6" t="n">
-        <v>79162</v>
+        <v>79166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128471245</v>
       </c>
       <c r="B7" t="n">
-        <v>79162</v>
+        <v>79166</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128471231</v>
       </c>
       <c r="B8" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128471250</v>
       </c>
       <c r="B9" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128471240</v>
       </c>
       <c r="B10" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128471228</v>
       </c>
       <c r="B11" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128471249</v>
       </c>
       <c r="B2" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128471247</v>
       </c>
       <c r="B3" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128471232</v>
       </c>
       <c r="B4" t="n">
-        <v>95433</v>
+        <v>95439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128471248</v>
       </c>
       <c r="B5" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128471231</v>
       </c>
       <c r="B8" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128471250</v>
       </c>
       <c r="B9" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128471228</v>
       </c>
       <c r="B11" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128471249</v>
       </c>
       <c r="B2" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128471247</v>
       </c>
       <c r="B3" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128471232</v>
       </c>
       <c r="B4" t="n">
-        <v>95439</v>
+        <v>95441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128471248</v>
       </c>
       <c r="B5" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128471246</v>
       </c>
       <c r="B6" t="n">
-        <v>79166</v>
+        <v>79168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128471245</v>
       </c>
       <c r="B7" t="n">
-        <v>79166</v>
+        <v>79168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128471231</v>
       </c>
       <c r="B8" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128471250</v>
       </c>
       <c r="B9" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128471240</v>
       </c>
       <c r="B10" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128471228</v>
       </c>
       <c r="B11" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128471249</v>
       </c>
       <c r="B2" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128471247</v>
       </c>
       <c r="B3" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128471232</v>
       </c>
       <c r="B4" t="n">
-        <v>95441</v>
+        <v>95442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128471248</v>
       </c>
       <c r="B5" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128471231</v>
       </c>
       <c r="B8" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128471250</v>
       </c>
       <c r="B9" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128471228</v>
       </c>
       <c r="B11" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128471249</v>
       </c>
       <c r="B2" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128471247</v>
       </c>
       <c r="B3" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128471232</v>
       </c>
       <c r="B4" t="n">
-        <v>95442</v>
+        <v>95469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128471248</v>
       </c>
       <c r="B5" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128471246</v>
       </c>
       <c r="B6" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128471245</v>
       </c>
       <c r="B7" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128471231</v>
       </c>
       <c r="B8" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128471250</v>
       </c>
       <c r="B9" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128471240</v>
       </c>
       <c r="B10" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128471228</v>
       </c>
       <c r="B11" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128471249</v>
       </c>
       <c r="B2" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128471247</v>
       </c>
       <c r="B3" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128471232</v>
       </c>
       <c r="B4" t="n">
-        <v>95469</v>
+        <v>95475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128471248</v>
       </c>
       <c r="B5" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128471246</v>
       </c>
       <c r="B6" t="n">
-        <v>79195</v>
+        <v>79199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128471245</v>
       </c>
       <c r="B7" t="n">
-        <v>79195</v>
+        <v>79199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128471231</v>
       </c>
       <c r="B8" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128471250</v>
       </c>
       <c r="B9" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128471240</v>
       </c>
       <c r="B10" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128471228</v>
       </c>
       <c r="B11" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128471249</v>
       </c>
       <c r="B2" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128471247</v>
       </c>
       <c r="B3" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128471232</v>
       </c>
       <c r="B4" t="n">
-        <v>95475</v>
+        <v>95482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128471248</v>
       </c>
       <c r="B5" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128471231</v>
       </c>
       <c r="B8" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128471250</v>
       </c>
       <c r="B9" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128471228</v>
       </c>
       <c r="B11" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128471249</v>
       </c>
       <c r="B2" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128471247</v>
       </c>
       <c r="B3" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128471232</v>
       </c>
       <c r="B4" t="n">
-        <v>95482</v>
+        <v>95486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128471248</v>
       </c>
       <c r="B5" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128471246</v>
       </c>
       <c r="B6" t="n">
-        <v>79199</v>
+        <v>79203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128471245</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79203</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128471231</v>
       </c>
       <c r="B8" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128471250</v>
       </c>
       <c r="B9" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128471240</v>
       </c>
       <c r="B10" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128471228</v>
       </c>
       <c r="B11" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128471249</v>
       </c>
       <c r="B2" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128471247</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128471232</v>
       </c>
       <c r="B4" t="n">
-        <v>95486</v>
+        <v>95493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128471248</v>
       </c>
       <c r="B5" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128471246</v>
       </c>
       <c r="B6" t="n">
-        <v>79203</v>
+        <v>79108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128471245</v>
       </c>
       <c r="B7" t="n">
-        <v>79203</v>
+        <v>79108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128471231</v>
       </c>
       <c r="B8" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128471250</v>
       </c>
       <c r="B9" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128471240</v>
       </c>
       <c r="B10" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128471228</v>
       </c>
       <c r="B11" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1643,6 +1643,103 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130213930</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97704</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>747942</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7457790</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>130213930</v>
       </c>
       <c r="B12" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>130213930</v>
       </c>
       <c r="B12" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>130213930</v>
       </c>
       <c r="B12" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>130213930</v>
       </c>
       <c r="B12" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>130213930</v>
       </c>
       <c r="B12" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>130213930</v>
       </c>
       <c r="B12" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2548-2021 artfynd.xlsx
+++ b/artfynd/A 2548-2021 artfynd.xlsx
@@ -1648,7 +1648,7 @@
         <v>130213930</v>
       </c>
       <c r="B12" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
